--- a/Lista vocabulario.xlsx
+++ b/Lista vocabulario.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Niños\Pablo Boronat\La Salle\10. 1ºESO\Deber y estudio\Inglés\App Vocabulary Pablo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5D1C4D-68E0-451A-BFE9-893D0DC5FC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DC81A0-9674-4A35-AAB6-40429723B21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D3A4DA7-A6CB-463D-B382-D9CDF113DD1D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="754">
   <si>
     <t>School utensils – Útiles escolares</t>
   </si>
@@ -2060,6 +2060,246 @@
   </si>
   <si>
     <t>Tema 09 - Verbs - Verbos</t>
+  </si>
+  <si>
+    <t>trip</t>
+  </si>
+  <si>
+    <t>excursión</t>
+  </si>
+  <si>
+    <t>arrive</t>
+  </si>
+  <si>
+    <t>llegar</t>
+  </si>
+  <si>
+    <t>try</t>
+  </si>
+  <si>
+    <t>intentar</t>
+  </si>
+  <si>
+    <t>present</t>
+  </si>
+  <si>
+    <t>regalo</t>
+  </si>
+  <si>
+    <t>amazing</t>
+  </si>
+  <si>
+    <t>sorprendente</t>
+  </si>
+  <si>
+    <t>spring</t>
+  </si>
+  <si>
+    <t>manantial</t>
+  </si>
+  <si>
+    <t>workshop</t>
+  </si>
+  <si>
+    <t>taller</t>
+  </si>
+  <si>
+    <t>dress up</t>
+  </si>
+  <si>
+    <t>report</t>
+  </si>
+  <si>
+    <t>informe</t>
+  </si>
+  <si>
+    <t>deep</t>
+  </si>
+  <si>
+    <t>profundo</t>
+  </si>
+  <si>
+    <t>heat</t>
+  </si>
+  <si>
+    <t>calor</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>Anno Domini / después de Cristo</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>época</t>
+  </si>
+  <si>
+    <t>pool</t>
+  </si>
+  <si>
+    <t>hot</t>
+  </si>
+  <si>
+    <t>caliente</t>
+  </si>
+  <si>
+    <t>warm</t>
+  </si>
+  <si>
+    <t>tibio</t>
+  </si>
+  <si>
+    <t>cold</t>
+  </si>
+  <si>
+    <t>frío</t>
+  </si>
+  <si>
+    <t>dome</t>
+  </si>
+  <si>
+    <t>cúpula</t>
+  </si>
+  <si>
+    <t>concrete</t>
+  </si>
+  <si>
+    <t>hormigón</t>
+  </si>
+  <si>
+    <t>hole</t>
+  </si>
+  <si>
+    <t>agujero</t>
+  </si>
+  <si>
+    <t>crowd</t>
+  </si>
+  <si>
+    <t>multitud</t>
+  </si>
+  <si>
+    <t>punishment</t>
+  </si>
+  <si>
+    <t>castigo</t>
+  </si>
+  <si>
+    <t>roof</t>
+  </si>
+  <si>
+    <t>tejado</t>
+  </si>
+  <si>
+    <t>marshy</t>
+  </si>
+  <si>
+    <t>pantanoso</t>
+  </si>
+  <si>
+    <t>wealthy</t>
+  </si>
+  <si>
+    <t>rico</t>
+  </si>
+  <si>
+    <t>forever</t>
+  </si>
+  <si>
+    <t>para siempre</t>
+  </si>
+  <si>
+    <t>to bury</t>
+  </si>
+  <si>
+    <t>enterrar</t>
+  </si>
+  <si>
+    <t>Tema 11 - Aedificae</t>
+  </si>
+  <si>
+    <t>Aedificae</t>
+  </si>
+  <si>
+    <t>Tema 12 - Lugares</t>
+  </si>
+  <si>
+    <t>Lugares</t>
+  </si>
+  <si>
+    <t>Library</t>
+  </si>
+  <si>
+    <t>Biblioteca</t>
+  </si>
+  <si>
+    <t>Football stadium</t>
+  </si>
+  <si>
+    <t>Estadio de fútbol</t>
+  </si>
+  <si>
+    <t>Post office</t>
+  </si>
+  <si>
+    <t>Oficina de correos</t>
+  </si>
+  <si>
+    <t>Teatro</t>
+  </si>
+  <si>
+    <t>Museum</t>
+  </si>
+  <si>
+    <t>Museo</t>
+  </si>
+  <si>
+    <t>Convenience store</t>
+  </si>
+  <si>
+    <t>Tienda de conveniencia</t>
+  </si>
+  <si>
+    <t>Bus station</t>
+  </si>
+  <si>
+    <t>Estación de autobuses</t>
+  </si>
+  <si>
+    <t>Shopping centre</t>
+  </si>
+  <si>
+    <t>Centro comercial</t>
+  </si>
+  <si>
+    <t>Bookshop</t>
+  </si>
+  <si>
+    <t>Librería</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>School</t>
+  </si>
+  <si>
+    <t>Escuela</t>
+  </si>
+  <si>
+    <t>Restaurant</t>
+  </si>
+  <si>
+    <t>Restaurante</t>
+  </si>
+  <si>
+    <t>Police station</t>
+  </si>
+  <si>
+    <t>Comisaría de policía</t>
   </si>
 </sst>
 </file>
@@ -2435,7 +2675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D353246F-5827-4F05-83D3-00EF78CCBDB0}">
-  <dimension ref="A1:H306"/>
+  <dimension ref="A1:H346"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -7080,7 +7320,7 @@
         <v>673</v>
       </c>
       <c r="H259" t="str">
-        <f t="shared" ref="H259:H267" si="4">CONCATENATE(E259," ","-"," ",F259)</f>
+        <f t="shared" ref="H259:H322" si="4">CONCATENATE(E259," ","-"," ",F259)</f>
         <v xml:space="preserve">Tema 09 - Verbs - Verbos - </v>
       </c>
     </row>
@@ -7217,6 +7457,10 @@
       <c r="E268" t="s">
         <v>623</v>
       </c>
+      <c r="H268" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
@@ -7228,6 +7472,10 @@
       <c r="E269" t="s">
         <v>623</v>
       </c>
+      <c r="H269" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
@@ -7239,6 +7487,10 @@
       <c r="E270" t="s">
         <v>623</v>
       </c>
+      <c r="H270" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
@@ -7250,6 +7502,10 @@
       <c r="E271" t="s">
         <v>623</v>
       </c>
+      <c r="H271" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
@@ -7261,8 +7517,12 @@
       <c r="E272" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H272" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>557</v>
       </c>
@@ -7272,8 +7532,12 @@
       <c r="E273" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H273" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>559</v>
       </c>
@@ -7283,8 +7547,12 @@
       <c r="E274" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H274" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>561</v>
       </c>
@@ -7294,8 +7562,12 @@
       <c r="E275" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H275" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>563</v>
       </c>
@@ -7305,8 +7577,12 @@
       <c r="E276" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H276" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>565</v>
       </c>
@@ -7316,8 +7592,12 @@
       <c r="E277" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H277" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>567</v>
       </c>
@@ -7327,8 +7607,12 @@
       <c r="E278" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H278" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>569</v>
       </c>
@@ -7338,8 +7622,12 @@
       <c r="E279" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H279" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>571</v>
       </c>
@@ -7349,8 +7637,12 @@
       <c r="E280" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H280" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>573</v>
       </c>
@@ -7360,8 +7652,12 @@
       <c r="E281" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H281" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>575</v>
       </c>
@@ -7371,8 +7667,12 @@
       <c r="E282" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H282" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>577</v>
       </c>
@@ -7382,8 +7682,12 @@
       <c r="E283" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H283" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>579</v>
       </c>
@@ -7393,8 +7697,12 @@
       <c r="E284" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H284" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>581</v>
       </c>
@@ -7404,8 +7712,12 @@
       <c r="E285" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H285" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>583</v>
       </c>
@@ -7415,8 +7727,12 @@
       <c r="E286" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H286" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>585</v>
       </c>
@@ -7426,8 +7742,12 @@
       <c r="E287" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H287" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>587</v>
       </c>
@@ -7437,8 +7757,12 @@
       <c r="E288" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H288" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>589</v>
       </c>
@@ -7448,8 +7772,12 @@
       <c r="E289" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H289" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>590</v>
       </c>
@@ -7459,8 +7787,12 @@
       <c r="E290" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H290" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>592</v>
       </c>
@@ -7470,8 +7802,12 @@
       <c r="E291" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H291" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>594</v>
       </c>
@@ -7481,8 +7817,12 @@
       <c r="E292" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H292" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>596</v>
       </c>
@@ -7492,8 +7832,12 @@
       <c r="E293" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H293" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>598</v>
       </c>
@@ -7503,8 +7847,12 @@
       <c r="E294" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H294" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>600</v>
       </c>
@@ -7514,8 +7862,12 @@
       <c r="E295" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H295" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>602</v>
       </c>
@@ -7525,8 +7877,12 @@
       <c r="E296" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H296" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>604</v>
       </c>
@@ -7536,8 +7892,12 @@
       <c r="E297" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H297" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>606</v>
       </c>
@@ -7547,8 +7907,12 @@
       <c r="E298" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H298" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>607</v>
       </c>
@@ -7558,8 +7922,12 @@
       <c r="E299" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H299" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>609</v>
       </c>
@@ -7569,8 +7937,12 @@
       <c r="E300" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H300" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>611</v>
       </c>
@@ -7580,8 +7952,12 @@
       <c r="E301" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H301" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>613</v>
       </c>
@@ -7591,8 +7967,12 @@
       <c r="E302" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H302" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>615</v>
       </c>
@@ -7602,8 +7982,12 @@
       <c r="E303" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H303" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>616</v>
       </c>
@@ -7613,8 +7997,12 @@
       <c r="E304" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H304" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>618</v>
       </c>
@@ -7624,8 +8012,12 @@
       <c r="E305" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H305" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>620</v>
       </c>
@@ -7634,6 +8026,730 @@
       </c>
       <c r="E306" t="s">
         <v>623</v>
+      </c>
+      <c r="H306" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">Tema 10 - Adjectives 2 - Adjectives to describe - </v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>674</v>
+      </c>
+      <c r="C307" t="s">
+        <v>675</v>
+      </c>
+      <c r="E307" t="s">
+        <v>726</v>
+      </c>
+      <c r="F307" t="s">
+        <v>727</v>
+      </c>
+      <c r="H307" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>676</v>
+      </c>
+      <c r="C308" t="s">
+        <v>677</v>
+      </c>
+      <c r="E308" t="s">
+        <v>726</v>
+      </c>
+      <c r="F308" t="s">
+        <v>727</v>
+      </c>
+      <c r="H308" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>678</v>
+      </c>
+      <c r="C309" t="s">
+        <v>679</v>
+      </c>
+      <c r="E309" t="s">
+        <v>726</v>
+      </c>
+      <c r="F309" t="s">
+        <v>727</v>
+      </c>
+      <c r="H309" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>680</v>
+      </c>
+      <c r="C310" t="s">
+        <v>681</v>
+      </c>
+      <c r="E310" t="s">
+        <v>726</v>
+      </c>
+      <c r="F310" t="s">
+        <v>727</v>
+      </c>
+      <c r="H310" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>682</v>
+      </c>
+      <c r="C311" t="s">
+        <v>683</v>
+      </c>
+      <c r="E311" t="s">
+        <v>726</v>
+      </c>
+      <c r="F311" t="s">
+        <v>727</v>
+      </c>
+      <c r="H311" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>684</v>
+      </c>
+      <c r="C312" t="s">
+        <v>685</v>
+      </c>
+      <c r="E312" t="s">
+        <v>726</v>
+      </c>
+      <c r="F312" t="s">
+        <v>727</v>
+      </c>
+      <c r="H312" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>686</v>
+      </c>
+      <c r="C313" t="s">
+        <v>687</v>
+      </c>
+      <c r="E313" t="s">
+        <v>726</v>
+      </c>
+      <c r="F313" t="s">
+        <v>727</v>
+      </c>
+      <c r="H313" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>688</v>
+      </c>
+      <c r="C314" t="s">
+        <v>525</v>
+      </c>
+      <c r="E314" t="s">
+        <v>726</v>
+      </c>
+      <c r="F314" t="s">
+        <v>727</v>
+      </c>
+      <c r="H314" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>689</v>
+      </c>
+      <c r="C315" t="s">
+        <v>690</v>
+      </c>
+      <c r="E315" t="s">
+        <v>726</v>
+      </c>
+      <c r="F315" t="s">
+        <v>727</v>
+      </c>
+      <c r="H315" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>691</v>
+      </c>
+      <c r="C316" t="s">
+        <v>692</v>
+      </c>
+      <c r="E316" t="s">
+        <v>726</v>
+      </c>
+      <c r="F316" t="s">
+        <v>727</v>
+      </c>
+      <c r="H316" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>693</v>
+      </c>
+      <c r="C317" t="s">
+        <v>694</v>
+      </c>
+      <c r="E317" t="s">
+        <v>726</v>
+      </c>
+      <c r="F317" t="s">
+        <v>727</v>
+      </c>
+      <c r="H317" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>695</v>
+      </c>
+      <c r="C318" t="s">
+        <v>696</v>
+      </c>
+      <c r="E318" t="s">
+        <v>726</v>
+      </c>
+      <c r="F318" t="s">
+        <v>727</v>
+      </c>
+      <c r="H318" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>697</v>
+      </c>
+      <c r="C319" t="s">
+        <v>698</v>
+      </c>
+      <c r="E319" t="s">
+        <v>726</v>
+      </c>
+      <c r="F319" t="s">
+        <v>727</v>
+      </c>
+      <c r="H319" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>699</v>
+      </c>
+      <c r="C320" t="s">
+        <v>63</v>
+      </c>
+      <c r="E320" t="s">
+        <v>726</v>
+      </c>
+      <c r="F320" t="s">
+        <v>727</v>
+      </c>
+      <c r="H320" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>700</v>
+      </c>
+      <c r="C321" t="s">
+        <v>701</v>
+      </c>
+      <c r="E321" t="s">
+        <v>726</v>
+      </c>
+      <c r="F321" t="s">
+        <v>727</v>
+      </c>
+      <c r="H321" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>702</v>
+      </c>
+      <c r="C322" t="s">
+        <v>703</v>
+      </c>
+      <c r="E322" t="s">
+        <v>726</v>
+      </c>
+      <c r="F322" t="s">
+        <v>727</v>
+      </c>
+      <c r="H322" t="str">
+        <f t="shared" si="4"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>704</v>
+      </c>
+      <c r="C323" t="s">
+        <v>705</v>
+      </c>
+      <c r="E323" t="s">
+        <v>726</v>
+      </c>
+      <c r="F323" t="s">
+        <v>727</v>
+      </c>
+      <c r="H323" t="str">
+        <f t="shared" ref="H323:H346" si="5">CONCATENATE(E323," ","-"," ",F323)</f>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>706</v>
+      </c>
+      <c r="C324" t="s">
+        <v>707</v>
+      </c>
+      <c r="E324" t="s">
+        <v>726</v>
+      </c>
+      <c r="F324" t="s">
+        <v>727</v>
+      </c>
+      <c r="H324" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>708</v>
+      </c>
+      <c r="C325" t="s">
+        <v>709</v>
+      </c>
+      <c r="E325" t="s">
+        <v>726</v>
+      </c>
+      <c r="F325" t="s">
+        <v>727</v>
+      </c>
+      <c r="H325" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>710</v>
+      </c>
+      <c r="C326" t="s">
+        <v>711</v>
+      </c>
+      <c r="E326" t="s">
+        <v>726</v>
+      </c>
+      <c r="F326" t="s">
+        <v>727</v>
+      </c>
+      <c r="H326" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>712</v>
+      </c>
+      <c r="C327" t="s">
+        <v>713</v>
+      </c>
+      <c r="E327" t="s">
+        <v>726</v>
+      </c>
+      <c r="F327" t="s">
+        <v>727</v>
+      </c>
+      <c r="H327" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>714</v>
+      </c>
+      <c r="C328" t="s">
+        <v>715</v>
+      </c>
+      <c r="E328" t="s">
+        <v>726</v>
+      </c>
+      <c r="F328" t="s">
+        <v>727</v>
+      </c>
+      <c r="H328" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>716</v>
+      </c>
+      <c r="C329" t="s">
+        <v>717</v>
+      </c>
+      <c r="E329" t="s">
+        <v>726</v>
+      </c>
+      <c r="F329" t="s">
+        <v>727</v>
+      </c>
+      <c r="H329" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>718</v>
+      </c>
+      <c r="C330" t="s">
+        <v>719</v>
+      </c>
+      <c r="E330" t="s">
+        <v>726</v>
+      </c>
+      <c r="F330" t="s">
+        <v>727</v>
+      </c>
+      <c r="H330" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>720</v>
+      </c>
+      <c r="C331" t="s">
+        <v>721</v>
+      </c>
+      <c r="E331" t="s">
+        <v>726</v>
+      </c>
+      <c r="F331" t="s">
+        <v>727</v>
+      </c>
+      <c r="H331" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>722</v>
+      </c>
+      <c r="C332" t="s">
+        <v>723</v>
+      </c>
+      <c r="E332" t="s">
+        <v>726</v>
+      </c>
+      <c r="F332" t="s">
+        <v>727</v>
+      </c>
+      <c r="H332" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>724</v>
+      </c>
+      <c r="C333" t="s">
+        <v>725</v>
+      </c>
+      <c r="E333" t="s">
+        <v>726</v>
+      </c>
+      <c r="F333" t="s">
+        <v>727</v>
+      </c>
+      <c r="H333" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 11 - Aedificae - Aedificae</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>730</v>
+      </c>
+      <c r="C334" t="s">
+        <v>731</v>
+      </c>
+      <c r="E334" t="s">
+        <v>728</v>
+      </c>
+      <c r="F334" t="s">
+        <v>729</v>
+      </c>
+      <c r="H334" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>732</v>
+      </c>
+      <c r="C335" t="s">
+        <v>733</v>
+      </c>
+      <c r="E335" t="s">
+        <v>728</v>
+      </c>
+      <c r="F335" t="s">
+        <v>729</v>
+      </c>
+      <c r="H335" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>734</v>
+      </c>
+      <c r="C336" t="s">
+        <v>735</v>
+      </c>
+      <c r="E336" t="s">
+        <v>728</v>
+      </c>
+      <c r="F336" t="s">
+        <v>729</v>
+      </c>
+      <c r="H336" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>52</v>
+      </c>
+      <c r="C337" t="s">
+        <v>736</v>
+      </c>
+      <c r="E337" t="s">
+        <v>728</v>
+      </c>
+      <c r="F337" t="s">
+        <v>729</v>
+      </c>
+      <c r="H337" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>737</v>
+      </c>
+      <c r="C338" t="s">
+        <v>738</v>
+      </c>
+      <c r="E338" t="s">
+        <v>728</v>
+      </c>
+      <c r="F338" t="s">
+        <v>729</v>
+      </c>
+      <c r="H338" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>739</v>
+      </c>
+      <c r="C339" t="s">
+        <v>740</v>
+      </c>
+      <c r="E339" t="s">
+        <v>728</v>
+      </c>
+      <c r="F339" t="s">
+        <v>729</v>
+      </c>
+      <c r="H339" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>741</v>
+      </c>
+      <c r="C340" t="s">
+        <v>742</v>
+      </c>
+      <c r="E340" t="s">
+        <v>728</v>
+      </c>
+      <c r="F340" t="s">
+        <v>729</v>
+      </c>
+      <c r="H340" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>743</v>
+      </c>
+      <c r="C341" t="s">
+        <v>744</v>
+      </c>
+      <c r="E341" t="s">
+        <v>728</v>
+      </c>
+      <c r="F341" t="s">
+        <v>729</v>
+      </c>
+      <c r="H341" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>745</v>
+      </c>
+      <c r="C342" t="s">
+        <v>746</v>
+      </c>
+      <c r="E342" t="s">
+        <v>728</v>
+      </c>
+      <c r="F342" t="s">
+        <v>729</v>
+      </c>
+      <c r="H342" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>747</v>
+      </c>
+      <c r="C343" t="s">
+        <v>747</v>
+      </c>
+      <c r="E343" t="s">
+        <v>728</v>
+      </c>
+      <c r="F343" t="s">
+        <v>729</v>
+      </c>
+      <c r="H343" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>748</v>
+      </c>
+      <c r="C344" t="s">
+        <v>749</v>
+      </c>
+      <c r="E344" t="s">
+        <v>728</v>
+      </c>
+      <c r="F344" t="s">
+        <v>729</v>
+      </c>
+      <c r="H344" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>750</v>
+      </c>
+      <c r="C345" t="s">
+        <v>751</v>
+      </c>
+      <c r="E345" t="s">
+        <v>728</v>
+      </c>
+      <c r="F345" t="s">
+        <v>729</v>
+      </c>
+      <c r="H345" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>752</v>
+      </c>
+      <c r="C346" t="s">
+        <v>753</v>
+      </c>
+      <c r="E346" t="s">
+        <v>728</v>
+      </c>
+      <c r="F346" t="s">
+        <v>729</v>
+      </c>
+      <c r="H346" t="str">
+        <f t="shared" si="5"/>
+        <v>Tema 12 - Lugares - Lugares</v>
       </c>
     </row>
   </sheetData>

--- a/Lista vocabulario.xlsx
+++ b/Lista vocabulario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Niños\Pablo Boronat\La Salle\10. 1ºESO\Deber y estudio\Inglés\App Vocabulary Pablo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DC81A0-9674-4A35-AAB6-40429723B21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59EA271B-9321-49A7-85E6-579C125D1877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D3A4DA7-A6CB-463D-B382-D9CDF113DD1D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="713">
   <si>
     <t>School utensils – Útiles escolares</t>
   </si>
@@ -967,9 +967,6 @@
     <t>guapa</t>
   </si>
   <si>
-    <t>Adjectives 1 - Adjetivos 1</t>
-  </si>
-  <si>
     <t>Sinónimo inglés</t>
   </si>
   <si>
@@ -1927,132 +1924,6 @@
     <t>Tema 05 - Parts of the body - Partes del cuerpo</t>
   </si>
   <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 1</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 2</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 3</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 4</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 5</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 6</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 7</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 8</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 9</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 10</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 11</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 12</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 13</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 14</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 15</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 16</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 17</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 18</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 19</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 20</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 21</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 22</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 23</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 24</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 25</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 26</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 27</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 28</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 29</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 30</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 31</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 32</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 33</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 34</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 35</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 36</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 37</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 38</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 39</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 40</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 41</t>
-  </si>
-  <si>
-    <t>Tema 06 - Adjectives 1 - Adjetivos 42</t>
-  </si>
-  <si>
     <t>Tema 07 - Clothes to describe - Ropa para describir</t>
   </si>
   <si>
@@ -2300,6 +2171,12 @@
   </si>
   <si>
     <t>Comisaría de policía</t>
+  </si>
+  <si>
+    <t>Adjectives 1</t>
+  </si>
+  <si>
+    <t>Tema 06 - Adjectives 1</t>
   </si>
 </sst>
 </file>
@@ -2692,7 +2569,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>45</v>
@@ -2715,7 +2592,7 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
@@ -2733,7 +2610,7 @@
         <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F3" t="s">
         <v>0</v>
@@ -2748,10 +2625,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F4" t="s">
         <v>0</v>
@@ -2769,7 +2646,7 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -2787,7 +2664,7 @@
         <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F6" t="s">
         <v>0</v>
@@ -2805,7 +2682,7 @@
         <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -2823,7 +2700,7 @@
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F8" t="s">
         <v>0</v>
@@ -2844,7 +2721,7 @@
         <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -2865,7 +2742,7 @@
         <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F10" t="s">
         <v>0</v>
@@ -2886,7 +2763,7 @@
         <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -2904,7 +2781,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F12" t="s">
         <v>0</v>
@@ -2925,7 +2802,7 @@
         <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -2943,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F14" t="s">
         <v>0</v>
@@ -2961,7 +2838,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
@@ -2979,7 +2856,7 @@
         <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F16" t="s">
         <v>0</v>
@@ -2997,7 +2874,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F17" t="s">
         <v>0</v>
@@ -3015,7 +2892,7 @@
         <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F18" t="s">
         <v>0</v>
@@ -3033,7 +2910,7 @@
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F19" t="s">
         <v>0</v>
@@ -3051,7 +2928,7 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F20" t="s">
         <v>0</v>
@@ -3066,13 +2943,13 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D21" t="s">
         <v>37</v>
       </c>
       <c r="E21" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F21" t="s">
         <v>0</v>
@@ -3090,7 +2967,7 @@
         <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F22" t="s">
         <v>49</v>
@@ -3108,7 +2985,7 @@
         <v>60</v>
       </c>
       <c r="E23" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F23" t="s">
         <v>49</v>
@@ -3129,7 +3006,7 @@
         <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F24" t="s">
         <v>49</v>
@@ -3147,7 +3024,7 @@
         <v>61</v>
       </c>
       <c r="E25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F25" t="s">
         <v>49</v>
@@ -3165,7 +3042,7 @@
         <v>62</v>
       </c>
       <c r="E26" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F26" t="s">
         <v>49</v>
@@ -3183,7 +3060,7 @@
         <v>63</v>
       </c>
       <c r="E27" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F27" t="s">
         <v>49</v>
@@ -3201,7 +3078,7 @@
         <v>64</v>
       </c>
       <c r="E28" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F28" t="s">
         <v>49</v>
@@ -3222,7 +3099,7 @@
         <v>68</v>
       </c>
       <c r="E29" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F29" t="s">
         <v>49</v>
@@ -3240,7 +3117,7 @@
         <v>65</v>
       </c>
       <c r="E30" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F30" t="s">
         <v>49</v>
@@ -3258,7 +3135,7 @@
         <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F31" t="s">
         <v>70</v>
@@ -3276,7 +3153,7 @@
         <v>86</v>
       </c>
       <c r="E32" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F32" t="s">
         <v>70</v>
@@ -3294,7 +3171,7 @@
         <v>87</v>
       </c>
       <c r="E33" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F33" t="s">
         <v>70</v>
@@ -3315,7 +3192,7 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F34" t="s">
         <v>70</v>
@@ -3333,7 +3210,7 @@
         <v>90</v>
       </c>
       <c r="E35" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F35" t="s">
         <v>70</v>
@@ -3354,7 +3231,7 @@
         <v>91</v>
       </c>
       <c r="E36" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F36" t="s">
         <v>70</v>
@@ -3372,7 +3249,7 @@
         <v>93</v>
       </c>
       <c r="E37" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F37" t="s">
         <v>70</v>
@@ -3390,7 +3267,7 @@
         <v>94</v>
       </c>
       <c r="E38" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F38" t="s">
         <v>70</v>
@@ -3408,7 +3285,7 @@
         <v>95</v>
       </c>
       <c r="E39" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F39" t="s">
         <v>70</v>
@@ -3426,7 +3303,7 @@
         <v>96</v>
       </c>
       <c r="E40" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F40" t="s">
         <v>70</v>
@@ -3444,7 +3321,7 @@
         <v>97</v>
       </c>
       <c r="E41" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F41" t="s">
         <v>70</v>
@@ -3462,7 +3339,7 @@
         <v>98</v>
       </c>
       <c r="E42" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F42" t="s">
         <v>70</v>
@@ -3480,7 +3357,7 @@
         <v>99</v>
       </c>
       <c r="E43" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F43" t="s">
         <v>70</v>
@@ -3498,7 +3375,7 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F44" t="s">
         <v>70</v>
@@ -3516,7 +3393,7 @@
         <v>138</v>
       </c>
       <c r="E45" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F45" t="s">
         <v>146</v>
@@ -3534,7 +3411,7 @@
         <v>139</v>
       </c>
       <c r="E46" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F46" t="s">
         <v>146</v>
@@ -3552,7 +3429,7 @@
         <v>140</v>
       </c>
       <c r="E47" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F47" t="s">
         <v>146</v>
@@ -3570,7 +3447,7 @@
         <v>141</v>
       </c>
       <c r="E48" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F48" t="s">
         <v>146</v>
@@ -3588,7 +3465,7 @@
         <v>142</v>
       </c>
       <c r="E49" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F49" t="s">
         <v>146</v>
@@ -3606,7 +3483,7 @@
         <v>143</v>
       </c>
       <c r="E50" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F50" t="s">
         <v>146</v>
@@ -3624,7 +3501,7 @@
         <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F51" t="s">
         <v>146</v>
@@ -3642,7 +3519,7 @@
         <v>145</v>
       </c>
       <c r="E52" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F52" t="s">
         <v>146</v>
@@ -3660,7 +3537,7 @@
         <v>135</v>
       </c>
       <c r="E53" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F53" t="s">
         <v>146</v>
@@ -3678,7 +3555,7 @@
         <v>136</v>
       </c>
       <c r="E54" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F54" t="s">
         <v>146</v>
@@ -3696,7 +3573,7 @@
         <v>137</v>
       </c>
       <c r="E55" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F55" t="s">
         <v>146</v>
@@ -3714,7 +3591,7 @@
         <v>125</v>
       </c>
       <c r="E56" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F56" t="s">
         <v>146</v>
@@ -3732,7 +3609,7 @@
         <v>134</v>
       </c>
       <c r="E57" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F57" t="s">
         <v>146</v>
@@ -3750,7 +3627,7 @@
         <v>126</v>
       </c>
       <c r="E58" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F58" t="s">
         <v>146</v>
@@ -3768,7 +3645,7 @@
         <v>132</v>
       </c>
       <c r="E59" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F59" t="s">
         <v>146</v>
@@ -3786,7 +3663,7 @@
         <v>133</v>
       </c>
       <c r="E60" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F60" t="s">
         <v>146</v>
@@ -3804,7 +3681,7 @@
         <v>127</v>
       </c>
       <c r="E61" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F61" t="s">
         <v>146</v>
@@ -3819,10 +3696,10 @@
         <v>118</v>
       </c>
       <c r="C62" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E62" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F62" t="s">
         <v>146</v>
@@ -3840,7 +3717,7 @@
         <v>119</v>
       </c>
       <c r="E63" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F63" t="s">
         <v>146</v>
@@ -3858,7 +3735,7 @@
         <v>128</v>
       </c>
       <c r="E64" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F64" t="s">
         <v>146</v>
@@ -3876,7 +3753,7 @@
         <v>129</v>
       </c>
       <c r="E65" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F65" t="s">
         <v>146</v>
@@ -3894,7 +3771,7 @@
         <v>130</v>
       </c>
       <c r="E66" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F66" t="s">
         <v>146</v>
@@ -3912,7 +3789,7 @@
         <v>131</v>
       </c>
       <c r="E67" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F67" t="s">
         <v>146</v>
@@ -3927,10 +3804,10 @@
         <v>124</v>
       </c>
       <c r="C68" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E68" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F68" t="s">
         <v>146</v>
@@ -3948,7 +3825,7 @@
         <v>156</v>
       </c>
       <c r="E69" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F69" t="s">
         <v>146</v>
@@ -3966,7 +3843,7 @@
         <v>157</v>
       </c>
       <c r="E70" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F70" t="s">
         <v>146</v>
@@ -3984,7 +3861,7 @@
         <v>149</v>
       </c>
       <c r="E71" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F71" t="s">
         <v>146</v>
@@ -4002,7 +3879,7 @@
         <v>158</v>
       </c>
       <c r="E72" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F72" t="s">
         <v>146</v>
@@ -4020,7 +3897,7 @@
         <v>159</v>
       </c>
       <c r="E73" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F73" t="s">
         <v>146</v>
@@ -4038,7 +3915,7 @@
         <v>160</v>
       </c>
       <c r="E74" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F74" t="s">
         <v>146</v>
@@ -4056,7 +3933,7 @@
         <v>161</v>
       </c>
       <c r="E75" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F75" t="s">
         <v>146</v>
@@ -4074,7 +3951,7 @@
         <v>162</v>
       </c>
       <c r="E76" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F76" t="s">
         <v>146</v>
@@ -4092,7 +3969,7 @@
         <v>163</v>
       </c>
       <c r="E77" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F77" t="s">
         <v>146</v>
@@ -4110,7 +3987,7 @@
         <v>165</v>
       </c>
       <c r="E78" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F78" t="s">
         <v>146</v>
@@ -4128,7 +4005,7 @@
         <v>198</v>
       </c>
       <c r="E79" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F79" t="s">
         <v>197</v>
@@ -4146,7 +4023,7 @@
         <v>199</v>
       </c>
       <c r="E80" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F80" t="s">
         <v>197</v>
@@ -4164,7 +4041,7 @@
         <v>200</v>
       </c>
       <c r="E81" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F81" t="s">
         <v>197</v>
@@ -4182,7 +4059,7 @@
         <v>201</v>
       </c>
       <c r="E82" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F82" t="s">
         <v>197</v>
@@ -4200,7 +4077,7 @@
         <v>171</v>
       </c>
       <c r="E83" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F83" t="s">
         <v>197</v>
@@ -4218,7 +4095,7 @@
         <v>202</v>
       </c>
       <c r="E84" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F84" t="s">
         <v>197</v>
@@ -4236,7 +4113,7 @@
         <v>203</v>
       </c>
       <c r="E85" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F85" t="s">
         <v>197</v>
@@ -4254,7 +4131,7 @@
         <v>204</v>
       </c>
       <c r="E86" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F86" t="s">
         <v>197</v>
@@ -4272,7 +4149,7 @@
         <v>205</v>
       </c>
       <c r="E87" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F87" t="s">
         <v>197</v>
@@ -4290,7 +4167,7 @@
         <v>206</v>
       </c>
       <c r="E88" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F88" t="s">
         <v>197</v>
@@ -4308,7 +4185,7 @@
         <v>207</v>
       </c>
       <c r="E89" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F89" t="s">
         <v>197</v>
@@ -4326,7 +4203,7 @@
         <v>208</v>
       </c>
       <c r="E90" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F90" t="s">
         <v>197</v>
@@ -4344,7 +4221,7 @@
         <v>209</v>
       </c>
       <c r="E91" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F91" t="s">
         <v>197</v>
@@ -4362,7 +4239,7 @@
         <v>210</v>
       </c>
       <c r="E92" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F92" t="s">
         <v>197</v>
@@ -4380,7 +4257,7 @@
         <v>226</v>
       </c>
       <c r="E93" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F93" t="s">
         <v>197</v>
@@ -4398,7 +4275,7 @@
         <v>211</v>
       </c>
       <c r="E94" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F94" t="s">
         <v>197</v>
@@ -4416,7 +4293,7 @@
         <v>212</v>
       </c>
       <c r="E95" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F95" t="s">
         <v>197</v>
@@ -4434,7 +4311,7 @@
         <v>213</v>
       </c>
       <c r="E96" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F96" t="s">
         <v>197</v>
@@ -4452,7 +4329,7 @@
         <v>214</v>
       </c>
       <c r="E97" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F97" t="s">
         <v>197</v>
@@ -4470,7 +4347,7 @@
         <v>215</v>
       </c>
       <c r="E98" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F98" t="s">
         <v>197</v>
@@ -4488,7 +4365,7 @@
         <v>216</v>
       </c>
       <c r="E99" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F99" t="s">
         <v>197</v>
@@ -4506,7 +4383,7 @@
         <v>217</v>
       </c>
       <c r="E100" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F100" t="s">
         <v>197</v>
@@ -4524,7 +4401,7 @@
         <v>218</v>
       </c>
       <c r="E101" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F101" t="s">
         <v>197</v>
@@ -4542,7 +4419,7 @@
         <v>219</v>
       </c>
       <c r="E102" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F102" t="s">
         <v>197</v>
@@ -4560,7 +4437,7 @@
         <v>220</v>
       </c>
       <c r="E103" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F103" t="s">
         <v>197</v>
@@ -4578,7 +4455,7 @@
         <v>225</v>
       </c>
       <c r="E104" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F104" t="s">
         <v>197</v>
@@ -4596,7 +4473,7 @@
         <v>221</v>
       </c>
       <c r="E105" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F105" t="s">
         <v>197</v>
@@ -4614,7 +4491,7 @@
         <v>224</v>
       </c>
       <c r="E106" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F106" t="s">
         <v>197</v>
@@ -4632,7 +4509,7 @@
         <v>222</v>
       </c>
       <c r="E107" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F107" t="s">
         <v>197</v>
@@ -4650,7 +4527,7 @@
         <v>223</v>
       </c>
       <c r="E108" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F108" t="s">
         <v>197</v>
@@ -4668,14 +4545,14 @@
         <v>269</v>
       </c>
       <c r="E109" t="s">
-        <v>629</v>
+        <v>712</v>
       </c>
       <c r="F109" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H109" t="str">
-        <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 1 - Adjectives 1 - Adjetivos 1</v>
+        <f>CONCATENATE(E109," ","-"," ",F109)</f>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
@@ -4686,14 +4563,14 @@
         <v>270</v>
       </c>
       <c r="E110" t="s">
-        <v>630</v>
+        <v>712</v>
       </c>
       <c r="F110" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H110" t="str">
-        <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 2 - Adjectives 1 - Adjetivos 1</v>
+        <f>CONCATENATE(E110," ","-"," ",F110)</f>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
@@ -4704,14 +4581,14 @@
         <v>271</v>
       </c>
       <c r="E111" t="s">
-        <v>631</v>
+        <v>712</v>
       </c>
       <c r="F111" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H111" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 3 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
@@ -4722,14 +4599,14 @@
         <v>272</v>
       </c>
       <c r="E112" t="s">
-        <v>632</v>
+        <v>712</v>
       </c>
       <c r="F112" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H112" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 4 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
@@ -4740,14 +4617,14 @@
         <v>273</v>
       </c>
       <c r="E113" t="s">
-        <v>633</v>
+        <v>712</v>
       </c>
       <c r="F113" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H113" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 5 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
@@ -4758,14 +4635,14 @@
         <v>274</v>
       </c>
       <c r="E114" t="s">
-        <v>634</v>
+        <v>712</v>
       </c>
       <c r="F114" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H114" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 6 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
@@ -4776,14 +4653,14 @@
         <v>275</v>
       </c>
       <c r="E115" t="s">
-        <v>635</v>
+        <v>712</v>
       </c>
       <c r="F115" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H115" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 7 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
@@ -4794,14 +4671,14 @@
         <v>276</v>
       </c>
       <c r="E116" t="s">
-        <v>636</v>
+        <v>712</v>
       </c>
       <c r="F116" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H116" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 8 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
@@ -4812,14 +4689,14 @@
         <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>637</v>
+        <v>712</v>
       </c>
       <c r="F117" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H117" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 9 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
@@ -4833,14 +4710,14 @@
         <v>307</v>
       </c>
       <c r="E118" t="s">
-        <v>638</v>
+        <v>712</v>
       </c>
       <c r="F118" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H118" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 10 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
@@ -4851,14 +4728,14 @@
         <v>279</v>
       </c>
       <c r="E119" t="s">
-        <v>639</v>
+        <v>712</v>
       </c>
       <c r="F119" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H119" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 11 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
@@ -4869,14 +4746,14 @@
         <v>280</v>
       </c>
       <c r="E120" t="s">
-        <v>640</v>
+        <v>712</v>
       </c>
       <c r="F120" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H120" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 12 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
@@ -4887,14 +4764,14 @@
         <v>281</v>
       </c>
       <c r="E121" t="s">
-        <v>641</v>
+        <v>712</v>
       </c>
       <c r="F121" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H121" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 13 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
@@ -4905,14 +4782,14 @@
         <v>306</v>
       </c>
       <c r="E122" t="s">
-        <v>642</v>
+        <v>712</v>
       </c>
       <c r="F122" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H122" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 14 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
@@ -4923,14 +4800,14 @@
         <v>282</v>
       </c>
       <c r="E123" t="s">
-        <v>643</v>
+        <v>712</v>
       </c>
       <c r="F123" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H123" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 15 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
@@ -4941,14 +4818,14 @@
         <v>283</v>
       </c>
       <c r="E124" t="s">
-        <v>644</v>
+        <v>712</v>
       </c>
       <c r="F124" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H124" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 16 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
@@ -4959,14 +4836,14 @@
         <v>284</v>
       </c>
       <c r="E125" t="s">
-        <v>645</v>
+        <v>712</v>
       </c>
       <c r="F125" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H125" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 17 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
@@ -4977,14 +4854,14 @@
         <v>285</v>
       </c>
       <c r="E126" t="s">
-        <v>646</v>
+        <v>712</v>
       </c>
       <c r="F126" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H126" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 18 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
@@ -4995,14 +4872,14 @@
         <v>286</v>
       </c>
       <c r="E127" t="s">
-        <v>647</v>
+        <v>712</v>
       </c>
       <c r="F127" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H127" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 19 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
@@ -5013,14 +4890,14 @@
         <v>287</v>
       </c>
       <c r="E128" t="s">
-        <v>648</v>
+        <v>712</v>
       </c>
       <c r="F128" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H128" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 20 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
@@ -5037,14 +4914,14 @@
         <v>278</v>
       </c>
       <c r="E129" t="s">
-        <v>649</v>
+        <v>712</v>
       </c>
       <c r="F129" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H129" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 21 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
@@ -5052,20 +4929,20 @@
         <v>248</v>
       </c>
       <c r="B130" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C130" t="s">
         <v>289</v>
       </c>
       <c r="E130" t="s">
-        <v>650</v>
+        <v>712</v>
       </c>
       <c r="F130" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H130" t="str">
         <f t="shared" si="1"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 22 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
@@ -5076,14 +4953,14 @@
         <v>290</v>
       </c>
       <c r="E131" t="s">
-        <v>651</v>
+        <v>712</v>
       </c>
       <c r="F131" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H131" t="str">
         <f t="shared" ref="H131:H194" si="2">CONCATENATE(E131," ","-"," ",F131)</f>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 23 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
@@ -5097,14 +4974,14 @@
         <v>308</v>
       </c>
       <c r="E132" t="s">
-        <v>652</v>
+        <v>712</v>
       </c>
       <c r="F132" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H132" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 24 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
@@ -5115,14 +4992,14 @@
         <v>292</v>
       </c>
       <c r="E133" t="s">
-        <v>653</v>
+        <v>712</v>
       </c>
       <c r="F133" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H133" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 25 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
@@ -5133,14 +5010,14 @@
         <v>291</v>
       </c>
       <c r="E134" t="s">
-        <v>654</v>
+        <v>712</v>
       </c>
       <c r="F134" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H134" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 26 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
@@ -5154,14 +5031,14 @@
         <v>278</v>
       </c>
       <c r="E135" t="s">
-        <v>655</v>
+        <v>712</v>
       </c>
       <c r="F135" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H135" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 27 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
@@ -5172,14 +5049,14 @@
         <v>293</v>
       </c>
       <c r="E136" t="s">
-        <v>656</v>
+        <v>712</v>
       </c>
       <c r="F136" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H136" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 28 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
@@ -5190,14 +5067,14 @@
         <v>294</v>
       </c>
       <c r="E137" t="s">
-        <v>657</v>
+        <v>712</v>
       </c>
       <c r="F137" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H137" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 29 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
@@ -5208,14 +5085,14 @@
         <v>295</v>
       </c>
       <c r="E138" t="s">
-        <v>658</v>
+        <v>712</v>
       </c>
       <c r="F138" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H138" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 30 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
@@ -5226,14 +5103,14 @@
         <v>296</v>
       </c>
       <c r="E139" t="s">
-        <v>659</v>
+        <v>712</v>
       </c>
       <c r="F139" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H139" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 31 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
@@ -5244,14 +5121,14 @@
         <v>297</v>
       </c>
       <c r="E140" t="s">
-        <v>660</v>
+        <v>712</v>
       </c>
       <c r="F140" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H140" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 32 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
@@ -5262,14 +5139,14 @@
         <v>298</v>
       </c>
       <c r="E141" t="s">
-        <v>661</v>
+        <v>712</v>
       </c>
       <c r="F141" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H141" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 33 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
@@ -5280,14 +5157,14 @@
         <v>299</v>
       </c>
       <c r="E142" t="s">
-        <v>662</v>
+        <v>712</v>
       </c>
       <c r="F142" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H142" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 34 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
@@ -5295,20 +5172,20 @@
         <v>261</v>
       </c>
       <c r="B143" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C143" t="s">
         <v>289</v>
       </c>
       <c r="E143" t="s">
-        <v>663</v>
+        <v>712</v>
       </c>
       <c r="F143" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H143" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 35 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
@@ -5319,14 +5196,14 @@
         <v>300</v>
       </c>
       <c r="E144" t="s">
-        <v>664</v>
+        <v>712</v>
       </c>
       <c r="F144" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H144" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 36 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
@@ -5337,14 +5214,14 @@
         <v>301</v>
       </c>
       <c r="E145" t="s">
-        <v>665</v>
+        <v>712</v>
       </c>
       <c r="F145" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H145" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 37 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
@@ -5352,20 +5229,20 @@
         <v>264</v>
       </c>
       <c r="B146" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C146" t="s">
         <v>289</v>
       </c>
       <c r="E146" t="s">
-        <v>666</v>
+        <v>712</v>
       </c>
       <c r="F146" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H146" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 38 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
@@ -5376,14 +5253,14 @@
         <v>302</v>
       </c>
       <c r="E147" t="s">
-        <v>667</v>
+        <v>712</v>
       </c>
       <c r="F147" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H147" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 39 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
@@ -5394,14 +5271,14 @@
         <v>303</v>
       </c>
       <c r="E148" t="s">
-        <v>668</v>
+        <v>712</v>
       </c>
       <c r="F148" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H148" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 40 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
@@ -5412,14 +5289,14 @@
         <v>304</v>
       </c>
       <c r="E149" t="s">
-        <v>669</v>
+        <v>712</v>
       </c>
       <c r="F149" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H149" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 41 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
@@ -5430,28 +5307,28 @@
         <v>305</v>
       </c>
       <c r="E150" t="s">
-        <v>670</v>
+        <v>712</v>
       </c>
       <c r="F150" t="s">
-        <v>309</v>
+        <v>711</v>
       </c>
       <c r="H150" t="str">
         <f t="shared" si="2"/>
-        <v>Tema 06 - Adjectives 1 - Adjetivos 42 - Adjectives 1 - Adjetivos 1</v>
+        <v>Tema 06 - Adjectives 1 - Adjectives 1</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C151" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E151" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F151" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H151" t="str">
         <f t="shared" si="2"/>
@@ -5460,16 +5337,16 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C152" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E152" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F152" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H152" t="str">
         <f t="shared" si="2"/>
@@ -5478,16 +5355,16 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C153" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E153" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F153" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H153" t="str">
         <f t="shared" si="2"/>
@@ -5496,16 +5373,16 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C154" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E154" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F154" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H154" t="str">
         <f t="shared" si="2"/>
@@ -5514,19 +5391,19 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B155" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C155" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E155" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F155" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H155" t="str">
         <f t="shared" si="2"/>
@@ -5535,16 +5412,16 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C156" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E156" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F156" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H156" t="str">
         <f t="shared" si="2"/>
@@ -5553,16 +5430,16 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C157" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E157" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F157" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H157" t="str">
         <f t="shared" si="2"/>
@@ -5571,16 +5448,16 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C158" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E158" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F158" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H158" t="str">
         <f t="shared" si="2"/>
@@ -5589,16 +5466,16 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C159" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E159" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F159" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H159" t="str">
         <f t="shared" si="2"/>
@@ -5607,16 +5484,16 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C160" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E160" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F160" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H160" t="str">
         <f t="shared" si="2"/>
@@ -5625,16 +5502,16 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C161" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E161" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F161" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H161" t="str">
         <f t="shared" si="2"/>
@@ -5643,22 +5520,22 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B162" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C162" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D162" t="s">
+        <v>363</v>
+      </c>
+      <c r="E162" t="s">
+        <v>628</v>
+      </c>
+      <c r="F162" t="s">
         <v>364</v>
-      </c>
-      <c r="E162" t="s">
-        <v>671</v>
-      </c>
-      <c r="F162" t="s">
-        <v>365</v>
       </c>
       <c r="H162" t="str">
         <f t="shared" si="2"/>
@@ -5667,16 +5544,16 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C163" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E163" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F163" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H163" t="str">
         <f t="shared" si="2"/>
@@ -5685,19 +5562,19 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>330</v>
+      </c>
+      <c r="B164" t="s">
         <v>331</v>
       </c>
-      <c r="B164" t="s">
-        <v>332</v>
-      </c>
       <c r="C164" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E164" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F164" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H164" t="str">
         <f t="shared" si="2"/>
@@ -5706,19 +5583,19 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B165" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C165" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E165" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F165" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H165" t="str">
         <f t="shared" si="2"/>
@@ -5727,16 +5604,16 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C166" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E166" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F166" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H166" t="str">
         <f t="shared" si="2"/>
@@ -5745,16 +5622,16 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C167" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E167" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F167" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H167" t="str">
         <f t="shared" si="2"/>
@@ -5763,16 +5640,16 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C168" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E168" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F168" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H168" t="str">
         <f t="shared" si="2"/>
@@ -5781,16 +5658,16 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C169" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E169" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F169" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H169" t="str">
         <f t="shared" si="2"/>
@@ -5799,16 +5676,16 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C170" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E170" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F170" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H170" t="str">
         <f t="shared" si="2"/>
@@ -5817,16 +5694,16 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C171" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E171" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F171" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H171" t="str">
         <f t="shared" si="2"/>
@@ -5835,16 +5712,16 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C172" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E172" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F172" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H172" t="str">
         <f t="shared" si="2"/>
@@ -5853,16 +5730,16 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C173" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E173" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F173" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H173" t="str">
         <f t="shared" si="2"/>
@@ -5871,16 +5748,16 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C174" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E174" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F174" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H174" t="str">
         <f t="shared" si="2"/>
@@ -5889,16 +5766,16 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C175" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E175" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
       <c r="F175" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H175" t="str">
         <f t="shared" si="2"/>
@@ -5907,16 +5784,16 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C176" t="s">
+        <v>363</v>
+      </c>
+      <c r="E176" t="s">
+        <v>628</v>
+      </c>
+      <c r="F176" t="s">
         <v>364</v>
-      </c>
-      <c r="E176" t="s">
-        <v>671</v>
-      </c>
-      <c r="F176" t="s">
-        <v>365</v>
       </c>
       <c r="H176" t="str">
         <f t="shared" si="2"/>
@@ -5925,16 +5802,16 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C177" t="s">
         <v>293</v>
       </c>
       <c r="E177" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F177" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H177" t="str">
         <f t="shared" si="2"/>
@@ -5943,16 +5820,16 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C178" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E178" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F178" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H178" t="str">
         <f t="shared" si="2"/>
@@ -5961,16 +5838,16 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C179" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E179" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F179" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H179" t="str">
         <f t="shared" si="2"/>
@@ -5979,16 +5856,16 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C180" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E180" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F180" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H180" t="str">
         <f t="shared" si="2"/>
@@ -5997,16 +5874,16 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C181" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E181" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F181" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H181" t="str">
         <f t="shared" si="2"/>
@@ -6015,16 +5892,16 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C182" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E182" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F182" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H182" t="str">
         <f t="shared" si="2"/>
@@ -6033,16 +5910,16 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C183" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E183" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F183" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H183" t="str">
         <f t="shared" si="2"/>
@@ -6051,16 +5928,16 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C184" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E184" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F184" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H184" t="str">
         <f t="shared" si="2"/>
@@ -6069,16 +5946,16 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C185" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E185" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F185" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H185" t="str">
         <f t="shared" si="2"/>
@@ -6087,16 +5964,16 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C186" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E186" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F186" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H186" t="str">
         <f t="shared" si="2"/>
@@ -6105,16 +5982,16 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C187" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E187" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F187" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H187" t="str">
         <f t="shared" si="2"/>
@@ -6123,16 +6000,16 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C188" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E188" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F188" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H188" t="str">
         <f t="shared" si="2"/>
@@ -6141,16 +6018,16 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C189" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E189" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F189" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H189" t="str">
         <f t="shared" si="2"/>
@@ -6159,16 +6036,16 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C190" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E190" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F190" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H190" t="str">
         <f t="shared" si="2"/>
@@ -6177,16 +6054,16 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C191" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E191" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F191" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H191" t="str">
         <f t="shared" si="2"/>
@@ -6195,16 +6072,16 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C192" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E192" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F192" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H192" t="str">
         <f t="shared" si="2"/>
@@ -6213,16 +6090,16 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C193" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E193" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F193" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H193" t="str">
         <f t="shared" si="2"/>
@@ -6231,16 +6108,16 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C194" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E194" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F194" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H194" t="str">
         <f t="shared" si="2"/>
@@ -6249,16 +6126,16 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C195" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E195" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F195" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H195" t="str">
         <f t="shared" ref="H195:H258" si="3">CONCATENATE(E195," ","-"," ",F195)</f>
@@ -6267,16 +6144,16 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C196" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E196" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F196" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H196" t="str">
         <f t="shared" si="3"/>
@@ -6285,16 +6162,16 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C197" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E197" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F197" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H197" t="str">
         <f t="shared" si="3"/>
@@ -6303,16 +6180,16 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C198" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E198" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F198" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H198" t="str">
         <f t="shared" si="3"/>
@@ -6321,16 +6198,16 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C199" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E199" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F199" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H199" t="str">
         <f t="shared" si="3"/>
@@ -6339,16 +6216,16 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C200" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E200" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F200" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H200" t="str">
         <f t="shared" si="3"/>
@@ -6357,16 +6234,16 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C201" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E201" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F201" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H201" t="str">
         <f t="shared" si="3"/>
@@ -6375,16 +6252,16 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C202" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E202" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F202" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H202" t="str">
         <f t="shared" si="3"/>
@@ -6393,16 +6270,16 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C203" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E203" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F203" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H203" t="str">
         <f t="shared" si="3"/>
@@ -6411,16 +6288,16 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C204" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E204" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F204" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H204" t="str">
         <f t="shared" si="3"/>
@@ -6429,16 +6306,16 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C205" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E205" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F205" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H205" t="str">
         <f t="shared" si="3"/>
@@ -6447,16 +6324,16 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E206" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F206" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H206" t="str">
         <f t="shared" si="3"/>
@@ -6465,16 +6342,16 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C207" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E207" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F207" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H207" t="str">
         <f t="shared" si="3"/>
@@ -6483,16 +6360,16 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C208" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E208" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F208" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H208" t="str">
         <f t="shared" si="3"/>
@@ -6501,16 +6378,16 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C209" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E209" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F209" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H209" t="str">
         <f t="shared" si="3"/>
@@ -6519,16 +6396,16 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C210" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E210" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F210" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H210" t="str">
         <f t="shared" si="3"/>
@@ -6537,16 +6414,16 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C211" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E211" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F211" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H211" t="str">
         <f t="shared" si="3"/>
@@ -6555,16 +6432,16 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C212" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E212" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F212" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H212" t="str">
         <f t="shared" si="3"/>
@@ -6573,16 +6450,16 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C213" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E213" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F213" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H213" t="str">
         <f t="shared" si="3"/>
@@ -6591,16 +6468,16 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C214" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E214" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F214" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H214" t="str">
         <f t="shared" si="3"/>
@@ -6609,16 +6486,16 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C215" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E215" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F215" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H215" t="str">
         <f t="shared" si="3"/>
@@ -6627,16 +6504,16 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C216" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E216" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F216" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H216" t="str">
         <f t="shared" si="3"/>
@@ -6645,16 +6522,16 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C217" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E217" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F217" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H217" t="str">
         <f t="shared" si="3"/>
@@ -6663,16 +6540,16 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C218" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E218" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F218" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H218" t="str">
         <f t="shared" si="3"/>
@@ -6681,16 +6558,16 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C219" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E219" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F219" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H219" t="str">
         <f t="shared" si="3"/>
@@ -6699,16 +6576,16 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C220" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E220" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F220" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H220" t="str">
         <f t="shared" si="3"/>
@@ -6717,16 +6594,16 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C221" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E221" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F221" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H221" t="str">
         <f t="shared" si="3"/>
@@ -6735,16 +6612,16 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C222" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E222" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F222" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H222" t="str">
         <f t="shared" si="3"/>
@@ -6753,16 +6630,16 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C223" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E223" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F223" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H223" t="str">
         <f t="shared" si="3"/>
@@ -6771,16 +6648,16 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C224" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E224" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F224" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H224" t="str">
         <f t="shared" si="3"/>
@@ -6789,16 +6666,16 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C225" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E225" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="F225" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H225" t="str">
         <f t="shared" si="3"/>
@@ -6807,16 +6684,16 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
+        <v>460</v>
+      </c>
+      <c r="C226" t="s">
+        <v>416</v>
+      </c>
+      <c r="E226" t="s">
+        <v>629</v>
+      </c>
+      <c r="F226" t="s">
         <v>461</v>
-      </c>
-      <c r="C226" t="s">
-        <v>417</v>
-      </c>
-      <c r="E226" t="s">
-        <v>672</v>
-      </c>
-      <c r="F226" t="s">
-        <v>462</v>
       </c>
       <c r="H226" t="str">
         <f t="shared" si="3"/>
@@ -6825,13 +6702,13 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
+        <v>463</v>
+      </c>
+      <c r="C227" t="s">
         <v>464</v>
       </c>
-      <c r="C227" t="s">
-        <v>465</v>
-      </c>
       <c r="E227" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H227" t="str">
         <f t="shared" si="3"/>
@@ -6840,13 +6717,13 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
+        <v>465</v>
+      </c>
+      <c r="C228" t="s">
         <v>466</v>
       </c>
-      <c r="C228" t="s">
-        <v>467</v>
-      </c>
       <c r="E228" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H228" t="str">
         <f t="shared" si="3"/>
@@ -6855,13 +6732,13 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
+        <v>467</v>
+      </c>
+      <c r="C229" t="s">
         <v>468</v>
       </c>
-      <c r="C229" t="s">
-        <v>469</v>
-      </c>
       <c r="E229" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H229" t="str">
         <f t="shared" si="3"/>
@@ -6870,13 +6747,13 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
+        <v>469</v>
+      </c>
+      <c r="C230" t="s">
         <v>470</v>
       </c>
-      <c r="C230" t="s">
-        <v>471</v>
-      </c>
       <c r="E230" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H230" t="str">
         <f t="shared" si="3"/>
@@ -6885,13 +6762,13 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
+        <v>471</v>
+      </c>
+      <c r="C231" t="s">
         <v>472</v>
       </c>
-      <c r="C231" t="s">
-        <v>473</v>
-      </c>
       <c r="E231" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H231" t="str">
         <f t="shared" si="3"/>
@@ -6900,13 +6777,13 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
+        <v>473</v>
+      </c>
+      <c r="C232" t="s">
         <v>474</v>
       </c>
-      <c r="C232" t="s">
-        <v>475</v>
-      </c>
       <c r="E232" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H232" t="str">
         <f t="shared" si="3"/>
@@ -6915,13 +6792,13 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
+        <v>475</v>
+      </c>
+      <c r="C233" t="s">
         <v>476</v>
       </c>
-      <c r="C233" t="s">
-        <v>477</v>
-      </c>
       <c r="E233" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H233" t="str">
         <f t="shared" si="3"/>
@@ -6930,13 +6807,13 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
+        <v>477</v>
+      </c>
+      <c r="C234" t="s">
         <v>478</v>
       </c>
-      <c r="C234" t="s">
-        <v>479</v>
-      </c>
       <c r="E234" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H234" t="str">
         <f t="shared" si="3"/>
@@ -6945,13 +6822,13 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
+        <v>479</v>
+      </c>
+      <c r="C235" t="s">
         <v>480</v>
       </c>
-      <c r="C235" t="s">
-        <v>481</v>
-      </c>
       <c r="E235" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H235" t="str">
         <f t="shared" si="3"/>
@@ -6960,13 +6837,13 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
+        <v>481</v>
+      </c>
+      <c r="C236" t="s">
         <v>482</v>
       </c>
-      <c r="C236" t="s">
-        <v>483</v>
-      </c>
       <c r="E236" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H236" t="str">
         <f t="shared" si="3"/>
@@ -6975,13 +6852,13 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
+        <v>483</v>
+      </c>
+      <c r="C237" t="s">
         <v>484</v>
       </c>
-      <c r="C237" t="s">
-        <v>485</v>
-      </c>
       <c r="E237" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H237" t="str">
         <f t="shared" si="3"/>
@@ -6990,13 +6867,13 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
+        <v>485</v>
+      </c>
+      <c r="C238" t="s">
         <v>486</v>
       </c>
-      <c r="C238" t="s">
-        <v>487</v>
-      </c>
       <c r="E238" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H238" t="str">
         <f t="shared" si="3"/>
@@ -7005,13 +6882,13 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
+        <v>487</v>
+      </c>
+      <c r="C239" t="s">
         <v>488</v>
       </c>
-      <c r="C239" t="s">
-        <v>489</v>
-      </c>
       <c r="E239" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H239" t="str">
         <f t="shared" si="3"/>
@@ -7020,13 +6897,13 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
+        <v>489</v>
+      </c>
+      <c r="C240" t="s">
         <v>490</v>
       </c>
-      <c r="C240" t="s">
-        <v>491</v>
-      </c>
       <c r="E240" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H240" t="str">
         <f t="shared" si="3"/>
@@ -7035,13 +6912,13 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
+        <v>491</v>
+      </c>
+      <c r="C241" t="s">
         <v>492</v>
       </c>
-      <c r="C241" t="s">
-        <v>493</v>
-      </c>
       <c r="E241" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H241" t="str">
         <f t="shared" si="3"/>
@@ -7050,13 +6927,13 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
+        <v>493</v>
+      </c>
+      <c r="C242" t="s">
         <v>494</v>
       </c>
-      <c r="C242" t="s">
-        <v>495</v>
-      </c>
       <c r="E242" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H242" t="str">
         <f t="shared" si="3"/>
@@ -7065,13 +6942,13 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
+        <v>495</v>
+      </c>
+      <c r="C243" t="s">
         <v>496</v>
       </c>
-      <c r="C243" t="s">
-        <v>497</v>
-      </c>
       <c r="E243" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H243" t="str">
         <f t="shared" si="3"/>
@@ -7080,13 +6957,13 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
+        <v>497</v>
+      </c>
+      <c r="C244" t="s">
         <v>498</v>
       </c>
-      <c r="C244" t="s">
-        <v>499</v>
-      </c>
       <c r="E244" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H244" t="str">
         <f t="shared" si="3"/>
@@ -7095,13 +6972,13 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
+        <v>499</v>
+      </c>
+      <c r="C245" t="s">
         <v>500</v>
       </c>
-      <c r="C245" t="s">
-        <v>501</v>
-      </c>
       <c r="E245" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H245" t="str">
         <f t="shared" si="3"/>
@@ -7110,13 +6987,13 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
+        <v>501</v>
+      </c>
+      <c r="C246" t="s">
         <v>502</v>
       </c>
-      <c r="C246" t="s">
-        <v>503</v>
-      </c>
       <c r="E246" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H246" t="str">
         <f t="shared" si="3"/>
@@ -7125,13 +7002,13 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
+        <v>503</v>
+      </c>
+      <c r="C247" t="s">
         <v>504</v>
       </c>
-      <c r="C247" t="s">
-        <v>505</v>
-      </c>
       <c r="E247" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H247" t="str">
         <f t="shared" si="3"/>
@@ -7140,16 +7017,16 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C248" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D248" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E248" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H248" t="str">
         <f t="shared" si="3"/>
@@ -7158,13 +7035,13 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
+        <v>506</v>
+      </c>
+      <c r="C249" t="s">
         <v>507</v>
       </c>
-      <c r="C249" t="s">
-        <v>508</v>
-      </c>
       <c r="E249" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H249" t="str">
         <f t="shared" si="3"/>
@@ -7173,13 +7050,13 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
+        <v>508</v>
+      </c>
+      <c r="C250" t="s">
         <v>509</v>
       </c>
-      <c r="C250" t="s">
-        <v>510</v>
-      </c>
       <c r="E250" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H250" t="str">
         <f t="shared" si="3"/>
@@ -7188,13 +7065,13 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
+        <v>510</v>
+      </c>
+      <c r="C251" t="s">
         <v>511</v>
       </c>
-      <c r="C251" t="s">
-        <v>512</v>
-      </c>
       <c r="E251" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H251" t="str">
         <f t="shared" si="3"/>
@@ -7203,13 +7080,13 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
+        <v>512</v>
+      </c>
+      <c r="C252" t="s">
         <v>513</v>
       </c>
-      <c r="C252" t="s">
-        <v>514</v>
-      </c>
       <c r="E252" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H252" t="str">
         <f t="shared" si="3"/>
@@ -7218,16 +7095,16 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C253" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D253" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E253" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H253" t="str">
         <f t="shared" si="3"/>
@@ -7236,13 +7113,13 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
+        <v>515</v>
+      </c>
+      <c r="C254" t="s">
         <v>516</v>
       </c>
-      <c r="C254" t="s">
-        <v>517</v>
-      </c>
       <c r="E254" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H254" t="str">
         <f t="shared" si="3"/>
@@ -7251,13 +7128,13 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
+        <v>517</v>
+      </c>
+      <c r="C255" t="s">
         <v>518</v>
       </c>
-      <c r="C255" t="s">
-        <v>519</v>
-      </c>
       <c r="E255" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H255" t="str">
         <f t="shared" si="3"/>
@@ -7266,13 +7143,13 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
+        <v>519</v>
+      </c>
+      <c r="C256" t="s">
         <v>520</v>
       </c>
-      <c r="C256" t="s">
-        <v>521</v>
-      </c>
       <c r="E256" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H256" t="str">
         <f t="shared" si="3"/>
@@ -7281,13 +7158,13 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
+        <v>521</v>
+      </c>
+      <c r="C257" t="s">
         <v>522</v>
       </c>
-      <c r="C257" t="s">
-        <v>523</v>
-      </c>
       <c r="E257" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H257" t="str">
         <f t="shared" si="3"/>
@@ -7296,13 +7173,13 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
+        <v>523</v>
+      </c>
+      <c r="C258" t="s">
         <v>524</v>
       </c>
-      <c r="C258" t="s">
-        <v>525</v>
-      </c>
       <c r="E258" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H258" t="str">
         <f t="shared" si="3"/>
@@ -7311,13 +7188,13 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
+        <v>525</v>
+      </c>
+      <c r="C259" t="s">
         <v>526</v>
       </c>
-      <c r="C259" t="s">
-        <v>527</v>
-      </c>
       <c r="E259" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H259" t="str">
         <f t="shared" ref="H259:H322" si="4">CONCATENATE(E259," ","-"," ",F259)</f>
@@ -7326,13 +7203,13 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
+        <v>527</v>
+      </c>
+      <c r="C260" t="s">
         <v>528</v>
       </c>
-      <c r="C260" t="s">
-        <v>529</v>
-      </c>
       <c r="E260" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H260" t="str">
         <f t="shared" si="4"/>
@@ -7341,13 +7218,13 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
+        <v>529</v>
+      </c>
+      <c r="C261" t="s">
         <v>530</v>
       </c>
-      <c r="C261" t="s">
-        <v>531</v>
-      </c>
       <c r="E261" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H261" t="str">
         <f t="shared" si="4"/>
@@ -7356,13 +7233,13 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
+        <v>531</v>
+      </c>
+      <c r="C262" t="s">
         <v>532</v>
       </c>
-      <c r="C262" t="s">
-        <v>533</v>
-      </c>
       <c r="E262" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H262" t="str">
         <f t="shared" si="4"/>
@@ -7371,13 +7248,13 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
+        <v>533</v>
+      </c>
+      <c r="C263" t="s">
         <v>534</v>
       </c>
-      <c r="C263" t="s">
-        <v>535</v>
-      </c>
       <c r="E263" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H263" t="str">
         <f t="shared" si="4"/>
@@ -7386,13 +7263,13 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
+        <v>535</v>
+      </c>
+      <c r="C264" t="s">
         <v>536</v>
       </c>
-      <c r="C264" t="s">
-        <v>537</v>
-      </c>
       <c r="E264" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H264" t="str">
         <f t="shared" si="4"/>
@@ -7401,13 +7278,13 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C265" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E265" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H265" t="str">
         <f t="shared" si="4"/>
@@ -7416,13 +7293,13 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
+        <v>538</v>
+      </c>
+      <c r="C266" t="s">
         <v>539</v>
       </c>
-      <c r="C266" t="s">
-        <v>540</v>
-      </c>
       <c r="E266" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="H266" t="str">
         <f t="shared" si="4"/>
@@ -7431,16 +7308,16 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
+        <v>544</v>
+      </c>
+      <c r="C267" t="s">
         <v>545</v>
       </c>
-      <c r="C267" t="s">
-        <v>546</v>
-      </c>
       <c r="E267" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F267" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H267" t="str">
         <f t="shared" si="4"/>
@@ -7449,13 +7326,13 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
+        <v>546</v>
+      </c>
+      <c r="C268" t="s">
         <v>547</v>
       </c>
-      <c r="C268" t="s">
-        <v>548</v>
-      </c>
       <c r="E268" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H268" t="str">
         <f t="shared" si="4"/>
@@ -7464,13 +7341,13 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
+        <v>548</v>
+      </c>
+      <c r="C269" t="s">
         <v>549</v>
       </c>
-      <c r="C269" t="s">
-        <v>550</v>
-      </c>
       <c r="E269" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H269" t="str">
         <f t="shared" si="4"/>
@@ -7479,13 +7356,13 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
+        <v>550</v>
+      </c>
+      <c r="C270" t="s">
         <v>551</v>
       </c>
-      <c r="C270" t="s">
-        <v>552</v>
-      </c>
       <c r="E270" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H270" t="str">
         <f t="shared" si="4"/>
@@ -7494,13 +7371,13 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
+        <v>552</v>
+      </c>
+      <c r="C271" t="s">
         <v>553</v>
       </c>
-      <c r="C271" t="s">
-        <v>554</v>
-      </c>
       <c r="E271" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H271" t="str">
         <f t="shared" si="4"/>
@@ -7509,13 +7386,13 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
+        <v>554</v>
+      </c>
+      <c r="C272" t="s">
         <v>555</v>
       </c>
-      <c r="C272" t="s">
-        <v>556</v>
-      </c>
       <c r="E272" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H272" t="str">
         <f t="shared" si="4"/>
@@ -7524,13 +7401,13 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
+        <v>556</v>
+      </c>
+      <c r="C273" t="s">
         <v>557</v>
       </c>
-      <c r="C273" t="s">
-        <v>558</v>
-      </c>
       <c r="E273" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H273" t="str">
         <f t="shared" si="4"/>
@@ -7539,13 +7416,13 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
+        <v>558</v>
+      </c>
+      <c r="C274" t="s">
         <v>559</v>
       </c>
-      <c r="C274" t="s">
-        <v>560</v>
-      </c>
       <c r="E274" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H274" t="str">
         <f t="shared" si="4"/>
@@ -7554,13 +7431,13 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
+        <v>560</v>
+      </c>
+      <c r="C275" t="s">
         <v>561</v>
       </c>
-      <c r="C275" t="s">
-        <v>562</v>
-      </c>
       <c r="E275" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H275" t="str">
         <f t="shared" si="4"/>
@@ -7569,13 +7446,13 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
+        <v>562</v>
+      </c>
+      <c r="C276" t="s">
         <v>563</v>
       </c>
-      <c r="C276" t="s">
-        <v>564</v>
-      </c>
       <c r="E276" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H276" t="str">
         <f t="shared" si="4"/>
@@ -7584,13 +7461,13 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
+        <v>564</v>
+      </c>
+      <c r="C277" t="s">
         <v>565</v>
       </c>
-      <c r="C277" t="s">
-        <v>566</v>
-      </c>
       <c r="E277" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H277" t="str">
         <f t="shared" si="4"/>
@@ -7599,13 +7476,13 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
+        <v>566</v>
+      </c>
+      <c r="C278" t="s">
         <v>567</v>
       </c>
-      <c r="C278" t="s">
-        <v>568</v>
-      </c>
       <c r="E278" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H278" t="str">
         <f t="shared" si="4"/>
@@ -7614,13 +7491,13 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
+        <v>568</v>
+      </c>
+      <c r="C279" t="s">
         <v>569</v>
       </c>
-      <c r="C279" t="s">
-        <v>570</v>
-      </c>
       <c r="E279" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H279" t="str">
         <f t="shared" si="4"/>
@@ -7629,13 +7506,13 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
+        <v>570</v>
+      </c>
+      <c r="C280" t="s">
         <v>571</v>
       </c>
-      <c r="C280" t="s">
-        <v>572</v>
-      </c>
       <c r="E280" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H280" t="str">
         <f t="shared" si="4"/>
@@ -7644,13 +7521,13 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
+        <v>572</v>
+      </c>
+      <c r="C281" t="s">
         <v>573</v>
       </c>
-      <c r="C281" t="s">
-        <v>574</v>
-      </c>
       <c r="E281" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H281" t="str">
         <f t="shared" si="4"/>
@@ -7659,13 +7536,13 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
+        <v>574</v>
+      </c>
+      <c r="C282" t="s">
         <v>575</v>
       </c>
-      <c r="C282" t="s">
-        <v>576</v>
-      </c>
       <c r="E282" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H282" t="str">
         <f t="shared" si="4"/>
@@ -7674,13 +7551,13 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
+        <v>576</v>
+      </c>
+      <c r="C283" t="s">
         <v>577</v>
       </c>
-      <c r="C283" t="s">
-        <v>578</v>
-      </c>
       <c r="E283" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H283" t="str">
         <f t="shared" si="4"/>
@@ -7689,13 +7566,13 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
+        <v>578</v>
+      </c>
+      <c r="C284" t="s">
         <v>579</v>
       </c>
-      <c r="C284" t="s">
-        <v>580</v>
-      </c>
       <c r="E284" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H284" t="str">
         <f t="shared" si="4"/>
@@ -7704,13 +7581,13 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
+        <v>580</v>
+      </c>
+      <c r="C285" t="s">
         <v>581</v>
       </c>
-      <c r="C285" t="s">
-        <v>582</v>
-      </c>
       <c r="E285" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H285" t="str">
         <f t="shared" si="4"/>
@@ -7719,13 +7596,13 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
+        <v>582</v>
+      </c>
+      <c r="C286" t="s">
         <v>583</v>
       </c>
-      <c r="C286" t="s">
-        <v>584</v>
-      </c>
       <c r="E286" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H286" t="str">
         <f t="shared" si="4"/>
@@ -7734,13 +7611,13 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
+        <v>584</v>
+      </c>
+      <c r="C287" t="s">
         <v>585</v>
       </c>
-      <c r="C287" t="s">
-        <v>586</v>
-      </c>
       <c r="E287" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H287" t="str">
         <f t="shared" si="4"/>
@@ -7749,13 +7626,13 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
+        <v>586</v>
+      </c>
+      <c r="C288" t="s">
         <v>587</v>
       </c>
-      <c r="C288" t="s">
-        <v>588</v>
-      </c>
       <c r="E288" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H288" t="str">
         <f t="shared" si="4"/>
@@ -7764,13 +7641,13 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C289" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E289" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H289" t="str">
         <f t="shared" si="4"/>
@@ -7779,13 +7656,13 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
+        <v>589</v>
+      </c>
+      <c r="C290" t="s">
         <v>590</v>
       </c>
-      <c r="C290" t="s">
-        <v>591</v>
-      </c>
       <c r="E290" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H290" t="str">
         <f t="shared" si="4"/>
@@ -7794,13 +7671,13 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
+        <v>591</v>
+      </c>
+      <c r="C291" t="s">
         <v>592</v>
       </c>
-      <c r="C291" t="s">
-        <v>593</v>
-      </c>
       <c r="E291" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H291" t="str">
         <f t="shared" si="4"/>
@@ -7809,13 +7686,13 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
+        <v>593</v>
+      </c>
+      <c r="C292" t="s">
         <v>594</v>
       </c>
-      <c r="C292" t="s">
-        <v>595</v>
-      </c>
       <c r="E292" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H292" t="str">
         <f t="shared" si="4"/>
@@ -7824,13 +7701,13 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
+        <v>595</v>
+      </c>
+      <c r="C293" t="s">
         <v>596</v>
       </c>
-      <c r="C293" t="s">
-        <v>597</v>
-      </c>
       <c r="E293" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H293" t="str">
         <f t="shared" si="4"/>
@@ -7839,13 +7716,13 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
+        <v>597</v>
+      </c>
+      <c r="C294" t="s">
         <v>598</v>
       </c>
-      <c r="C294" t="s">
-        <v>599</v>
-      </c>
       <c r="E294" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H294" t="str">
         <f t="shared" si="4"/>
@@ -7854,13 +7731,13 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
+        <v>599</v>
+      </c>
+      <c r="C295" t="s">
         <v>600</v>
       </c>
-      <c r="C295" t="s">
-        <v>601</v>
-      </c>
       <c r="E295" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H295" t="str">
         <f t="shared" si="4"/>
@@ -7869,13 +7746,13 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
+        <v>601</v>
+      </c>
+      <c r="C296" t="s">
         <v>602</v>
       </c>
-      <c r="C296" t="s">
-        <v>603</v>
-      </c>
       <c r="E296" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H296" t="str">
         <f t="shared" si="4"/>
@@ -7884,13 +7761,13 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
+        <v>603</v>
+      </c>
+      <c r="C297" t="s">
         <v>604</v>
       </c>
-      <c r="C297" t="s">
-        <v>605</v>
-      </c>
       <c r="E297" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H297" t="str">
         <f t="shared" si="4"/>
@@ -7899,13 +7776,13 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C298" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E298" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H298" t="str">
         <f t="shared" si="4"/>
@@ -7914,13 +7791,13 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
+        <v>606</v>
+      </c>
+      <c r="C299" t="s">
         <v>607</v>
       </c>
-      <c r="C299" t="s">
-        <v>608</v>
-      </c>
       <c r="E299" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H299" t="str">
         <f t="shared" si="4"/>
@@ -7929,13 +7806,13 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
+        <v>608</v>
+      </c>
+      <c r="C300" t="s">
         <v>609</v>
       </c>
-      <c r="C300" t="s">
-        <v>610</v>
-      </c>
       <c r="E300" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H300" t="str">
         <f t="shared" si="4"/>
@@ -7944,13 +7821,13 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
+        <v>610</v>
+      </c>
+      <c r="C301" t="s">
         <v>611</v>
       </c>
-      <c r="C301" t="s">
-        <v>612</v>
-      </c>
       <c r="E301" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H301" t="str">
         <f t="shared" si="4"/>
@@ -7959,13 +7836,13 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
+        <v>612</v>
+      </c>
+      <c r="C302" t="s">
         <v>613</v>
       </c>
-      <c r="C302" t="s">
-        <v>614</v>
-      </c>
       <c r="E302" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H302" t="str">
         <f t="shared" si="4"/>
@@ -7974,13 +7851,13 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C303" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E303" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H303" t="str">
         <f t="shared" si="4"/>
@@ -7989,13 +7866,13 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
+        <v>615</v>
+      </c>
+      <c r="C304" t="s">
         <v>616</v>
       </c>
-      <c r="C304" t="s">
-        <v>617</v>
-      </c>
       <c r="E304" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H304" t="str">
         <f t="shared" si="4"/>
@@ -8004,13 +7881,13 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
+        <v>617</v>
+      </c>
+      <c r="C305" t="s">
         <v>618</v>
       </c>
-      <c r="C305" t="s">
-        <v>619</v>
-      </c>
       <c r="E305" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H305" t="str">
         <f t="shared" si="4"/>
@@ -8019,13 +7896,13 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
+        <v>619</v>
+      </c>
+      <c r="C306" t="s">
         <v>620</v>
       </c>
-      <c r="C306" t="s">
-        <v>621</v>
-      </c>
       <c r="E306" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H306" t="str">
         <f t="shared" si="4"/>
@@ -8034,16 +7911,16 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>674</v>
+        <v>631</v>
       </c>
       <c r="C307" t="s">
-        <v>675</v>
+        <v>632</v>
       </c>
       <c r="E307" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F307" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H307" t="str">
         <f t="shared" si="4"/>
@@ -8052,16 +7929,16 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>676</v>
+        <v>633</v>
       </c>
       <c r="C308" t="s">
-        <v>677</v>
+        <v>634</v>
       </c>
       <c r="E308" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F308" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H308" t="str">
         <f t="shared" si="4"/>
@@ -8070,16 +7947,16 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>678</v>
+        <v>635</v>
       </c>
       <c r="C309" t="s">
-        <v>679</v>
+        <v>636</v>
       </c>
       <c r="E309" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F309" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H309" t="str">
         <f t="shared" si="4"/>
@@ -8088,16 +7965,16 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>680</v>
+        <v>637</v>
       </c>
       <c r="C310" t="s">
-        <v>681</v>
+        <v>638</v>
       </c>
       <c r="E310" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F310" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H310" t="str">
         <f t="shared" si="4"/>
@@ -8106,16 +7983,16 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>682</v>
+        <v>639</v>
       </c>
       <c r="C311" t="s">
+        <v>640</v>
+      </c>
+      <c r="E311" t="s">
         <v>683</v>
       </c>
-      <c r="E311" t="s">
-        <v>726</v>
-      </c>
       <c r="F311" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H311" t="str">
         <f t="shared" si="4"/>
@@ -8124,16 +8001,16 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
+        <v>641</v>
+      </c>
+      <c r="C312" t="s">
+        <v>642</v>
+      </c>
+      <c r="E312" t="s">
+        <v>683</v>
+      </c>
+      <c r="F312" t="s">
         <v>684</v>
-      </c>
-      <c r="C312" t="s">
-        <v>685</v>
-      </c>
-      <c r="E312" t="s">
-        <v>726</v>
-      </c>
-      <c r="F312" t="s">
-        <v>727</v>
       </c>
       <c r="H312" t="str">
         <f t="shared" si="4"/>
@@ -8142,16 +8019,16 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>686</v>
+        <v>643</v>
       </c>
       <c r="C313" t="s">
-        <v>687</v>
+        <v>644</v>
       </c>
       <c r="E313" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F313" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H313" t="str">
         <f t="shared" si="4"/>
@@ -8160,16 +8037,16 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>688</v>
+        <v>645</v>
       </c>
       <c r="C314" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E314" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F314" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H314" t="str">
         <f t="shared" si="4"/>
@@ -8178,16 +8055,16 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>689</v>
+        <v>646</v>
       </c>
       <c r="C315" t="s">
-        <v>690</v>
+        <v>647</v>
       </c>
       <c r="E315" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F315" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H315" t="str">
         <f t="shared" si="4"/>
@@ -8196,16 +8073,16 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>691</v>
+        <v>648</v>
       </c>
       <c r="C316" t="s">
-        <v>692</v>
+        <v>649</v>
       </c>
       <c r="E316" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F316" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H316" t="str">
         <f t="shared" si="4"/>
@@ -8214,16 +8091,16 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>693</v>
+        <v>650</v>
       </c>
       <c r="C317" t="s">
-        <v>694</v>
+        <v>651</v>
       </c>
       <c r="E317" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F317" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H317" t="str">
         <f t="shared" si="4"/>
@@ -8232,16 +8109,16 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>695</v>
+        <v>652</v>
       </c>
       <c r="C318" t="s">
-        <v>696</v>
+        <v>653</v>
       </c>
       <c r="E318" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F318" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H318" t="str">
         <f t="shared" si="4"/>
@@ -8250,16 +8127,16 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>697</v>
+        <v>654</v>
       </c>
       <c r="C319" t="s">
-        <v>698</v>
+        <v>655</v>
       </c>
       <c r="E319" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F319" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H319" t="str">
         <f t="shared" si="4"/>
@@ -8268,16 +8145,16 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>699</v>
+        <v>656</v>
       </c>
       <c r="C320" t="s">
         <v>63</v>
       </c>
       <c r="E320" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F320" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H320" t="str">
         <f t="shared" si="4"/>
@@ -8286,16 +8163,16 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>700</v>
+        <v>657</v>
       </c>
       <c r="C321" t="s">
-        <v>701</v>
+        <v>658</v>
       </c>
       <c r="E321" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F321" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H321" t="str">
         <f t="shared" si="4"/>
@@ -8304,16 +8181,16 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>702</v>
+        <v>659</v>
       </c>
       <c r="C322" t="s">
-        <v>703</v>
+        <v>660</v>
       </c>
       <c r="E322" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F322" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H322" t="str">
         <f t="shared" si="4"/>
@@ -8322,16 +8199,16 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>704</v>
+        <v>661</v>
       </c>
       <c r="C323" t="s">
-        <v>705</v>
+        <v>662</v>
       </c>
       <c r="E323" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F323" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H323" t="str">
         <f t="shared" ref="H323:H346" si="5">CONCATENATE(E323," ","-"," ",F323)</f>
@@ -8340,16 +8217,16 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>706</v>
+        <v>663</v>
       </c>
       <c r="C324" t="s">
-        <v>707</v>
+        <v>664</v>
       </c>
       <c r="E324" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F324" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H324" t="str">
         <f t="shared" si="5"/>
@@ -8358,16 +8235,16 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>708</v>
+        <v>665</v>
       </c>
       <c r="C325" t="s">
-        <v>709</v>
+        <v>666</v>
       </c>
       <c r="E325" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F325" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H325" t="str">
         <f t="shared" si="5"/>
@@ -8376,16 +8253,16 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>710</v>
+        <v>667</v>
       </c>
       <c r="C326" t="s">
-        <v>711</v>
+        <v>668</v>
       </c>
       <c r="E326" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F326" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H326" t="str">
         <f t="shared" si="5"/>
@@ -8394,16 +8271,16 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>712</v>
+        <v>669</v>
       </c>
       <c r="C327" t="s">
-        <v>713</v>
+        <v>670</v>
       </c>
       <c r="E327" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F327" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H327" t="str">
         <f t="shared" si="5"/>
@@ -8412,16 +8289,16 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>714</v>
+        <v>671</v>
       </c>
       <c r="C328" t="s">
-        <v>715</v>
+        <v>672</v>
       </c>
       <c r="E328" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F328" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H328" t="str">
         <f t="shared" si="5"/>
@@ -8430,16 +8307,16 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>716</v>
+        <v>673</v>
       </c>
       <c r="C329" t="s">
-        <v>717</v>
+        <v>674</v>
       </c>
       <c r="E329" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F329" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H329" t="str">
         <f t="shared" si="5"/>
@@ -8448,16 +8325,16 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>718</v>
+        <v>675</v>
       </c>
       <c r="C330" t="s">
-        <v>719</v>
+        <v>676</v>
       </c>
       <c r="E330" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F330" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H330" t="str">
         <f t="shared" si="5"/>
@@ -8466,16 +8343,16 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>720</v>
+        <v>677</v>
       </c>
       <c r="C331" t="s">
-        <v>721</v>
+        <v>678</v>
       </c>
       <c r="E331" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F331" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H331" t="str">
         <f t="shared" si="5"/>
@@ -8484,16 +8361,16 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>722</v>
+        <v>679</v>
       </c>
       <c r="C332" t="s">
-        <v>723</v>
+        <v>680</v>
       </c>
       <c r="E332" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F332" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H332" t="str">
         <f t="shared" si="5"/>
@@ -8502,16 +8379,16 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>724</v>
+        <v>681</v>
       </c>
       <c r="C333" t="s">
-        <v>725</v>
+        <v>682</v>
       </c>
       <c r="E333" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F333" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="H333" t="str">
         <f t="shared" si="5"/>
@@ -8520,16 +8397,16 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>730</v>
+        <v>687</v>
       </c>
       <c r="C334" t="s">
-        <v>731</v>
+        <v>688</v>
       </c>
       <c r="E334" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F334" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H334" t="str">
         <f t="shared" si="5"/>
@@ -8538,16 +8415,16 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>732</v>
+        <v>689</v>
       </c>
       <c r="C335" t="s">
-        <v>733</v>
+        <v>690</v>
       </c>
       <c r="E335" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F335" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H335" t="str">
         <f t="shared" si="5"/>
@@ -8556,16 +8433,16 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>734</v>
+        <v>691</v>
       </c>
       <c r="C336" t="s">
-        <v>735</v>
+        <v>692</v>
       </c>
       <c r="E336" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F336" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H336" t="str">
         <f t="shared" si="5"/>
@@ -8577,13 +8454,13 @@
         <v>52</v>
       </c>
       <c r="C337" t="s">
-        <v>736</v>
+        <v>693</v>
       </c>
       <c r="E337" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F337" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H337" t="str">
         <f t="shared" si="5"/>
@@ -8592,16 +8469,16 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>737</v>
+        <v>694</v>
       </c>
       <c r="C338" t="s">
-        <v>738</v>
+        <v>695</v>
       </c>
       <c r="E338" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F338" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H338" t="str">
         <f t="shared" si="5"/>
@@ -8610,16 +8487,16 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>739</v>
+        <v>696</v>
       </c>
       <c r="C339" t="s">
-        <v>740</v>
+        <v>697</v>
       </c>
       <c r="E339" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F339" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H339" t="str">
         <f t="shared" si="5"/>
@@ -8628,16 +8505,16 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>741</v>
+        <v>698</v>
       </c>
       <c r="C340" t="s">
-        <v>742</v>
+        <v>699</v>
       </c>
       <c r="E340" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F340" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H340" t="str">
         <f t="shared" si="5"/>
@@ -8646,16 +8523,16 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>743</v>
+        <v>700</v>
       </c>
       <c r="C341" t="s">
-        <v>744</v>
+        <v>701</v>
       </c>
       <c r="E341" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F341" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H341" t="str">
         <f t="shared" si="5"/>
@@ -8664,16 +8541,16 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>745</v>
+        <v>702</v>
       </c>
       <c r="C342" t="s">
-        <v>746</v>
+        <v>703</v>
       </c>
       <c r="E342" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F342" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H342" t="str">
         <f t="shared" si="5"/>
@@ -8682,16 +8559,16 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>747</v>
+        <v>704</v>
       </c>
       <c r="C343" t="s">
-        <v>747</v>
+        <v>704</v>
       </c>
       <c r="E343" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F343" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H343" t="str">
         <f t="shared" si="5"/>
@@ -8700,16 +8577,16 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>748</v>
+        <v>705</v>
       </c>
       <c r="C344" t="s">
-        <v>749</v>
+        <v>706</v>
       </c>
       <c r="E344" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F344" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H344" t="str">
         <f t="shared" si="5"/>
@@ -8718,16 +8595,16 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>750</v>
+        <v>707</v>
       </c>
       <c r="C345" t="s">
-        <v>751</v>
+        <v>708</v>
       </c>
       <c r="E345" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F345" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H345" t="str">
         <f t="shared" si="5"/>
@@ -8736,16 +8613,16 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>752</v>
+        <v>709</v>
       </c>
       <c r="C346" t="s">
-        <v>753</v>
+        <v>710</v>
       </c>
       <c r="E346" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="F346" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="H346" t="str">
         <f t="shared" si="5"/>
@@ -8774,322 +8651,322 @@
     </row>
     <row r="7" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E7" t="s">
+        <v>544</v>
+      </c>
+      <c r="F7" t="s">
         <v>545</v>
-      </c>
-      <c r="F7" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="8" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E8" t="s">
+        <v>546</v>
+      </c>
+      <c r="F8" t="s">
         <v>547</v>
-      </c>
-      <c r="F8" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="9" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E9" t="s">
+        <v>548</v>
+      </c>
+      <c r="F9" t="s">
         <v>549</v>
-      </c>
-      <c r="F9" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="10" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E10" t="s">
+        <v>550</v>
+      </c>
+      <c r="F10" t="s">
         <v>551</v>
-      </c>
-      <c r="F10" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="11" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E11" t="s">
+        <v>552</v>
+      </c>
+      <c r="F11" t="s">
         <v>553</v>
-      </c>
-      <c r="F11" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="12" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E12" t="s">
+        <v>554</v>
+      </c>
+      <c r="F12" t="s">
         <v>555</v>
-      </c>
-      <c r="F12" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="13" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E13" t="s">
+        <v>556</v>
+      </c>
+      <c r="F13" t="s">
         <v>557</v>
-      </c>
-      <c r="F13" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="14" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E14" t="s">
+        <v>558</v>
+      </c>
+      <c r="F14" t="s">
         <v>559</v>
-      </c>
-      <c r="F14" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="15" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E15" t="s">
+        <v>560</v>
+      </c>
+      <c r="F15" t="s">
         <v>561</v>
-      </c>
-      <c r="F15" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="16" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E16" t="s">
+        <v>562</v>
+      </c>
+      <c r="F16" t="s">
         <v>563</v>
-      </c>
-      <c r="F16" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="17" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E17" t="s">
+        <v>564</v>
+      </c>
+      <c r="F17" t="s">
         <v>565</v>
-      </c>
-      <c r="F17" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="18" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E18" t="s">
+        <v>566</v>
+      </c>
+      <c r="F18" t="s">
         <v>567</v>
-      </c>
-      <c r="F18" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="19" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E19" t="s">
+        <v>568</v>
+      </c>
+      <c r="F19" t="s">
         <v>569</v>
-      </c>
-      <c r="F19" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="20" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E20" t="s">
+        <v>570</v>
+      </c>
+      <c r="F20" t="s">
         <v>571</v>
-      </c>
-      <c r="F20" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="21" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E21" t="s">
+        <v>572</v>
+      </c>
+      <c r="F21" t="s">
         <v>573</v>
-      </c>
-      <c r="F21" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="22" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E22" t="s">
+        <v>574</v>
+      </c>
+      <c r="F22" t="s">
         <v>575</v>
-      </c>
-      <c r="F22" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E23" t="s">
+        <v>576</v>
+      </c>
+      <c r="F23" t="s">
         <v>577</v>
-      </c>
-      <c r="F23" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="24" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E24" t="s">
+        <v>578</v>
+      </c>
+      <c r="F24" t="s">
         <v>579</v>
-      </c>
-      <c r="F24" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E25" t="s">
+        <v>580</v>
+      </c>
+      <c r="F25" t="s">
         <v>581</v>
-      </c>
-      <c r="F25" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E26" t="s">
+        <v>582</v>
+      </c>
+      <c r="F26" t="s">
         <v>583</v>
-      </c>
-      <c r="F26" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="27" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E27" t="s">
+        <v>584</v>
+      </c>
+      <c r="F27" t="s">
         <v>585</v>
-      </c>
-      <c r="F27" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="28" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E28" t="s">
+        <v>586</v>
+      </c>
+      <c r="F28" t="s">
         <v>587</v>
-      </c>
-      <c r="F28" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="29" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E29" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F29" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="30" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E30" t="s">
+        <v>589</v>
+      </c>
+      <c r="F30" t="s">
         <v>590</v>
-      </c>
-      <c r="F30" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="31" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E31" t="s">
+        <v>591</v>
+      </c>
+      <c r="F31" t="s">
         <v>592</v>
-      </c>
-      <c r="F31" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="32" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E32" t="s">
+        <v>593</v>
+      </c>
+      <c r="F32" t="s">
         <v>594</v>
-      </c>
-      <c r="F32" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="33" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E33" t="s">
+        <v>595</v>
+      </c>
+      <c r="F33" t="s">
         <v>596</v>
-      </c>
-      <c r="F33" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="34" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E34" t="s">
+        <v>597</v>
+      </c>
+      <c r="F34" t="s">
         <v>598</v>
-      </c>
-      <c r="F34" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="35" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E35" t="s">
+        <v>599</v>
+      </c>
+      <c r="F35" t="s">
         <v>600</v>
-      </c>
-      <c r="F35" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="36" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E36" t="s">
+        <v>601</v>
+      </c>
+      <c r="F36" t="s">
         <v>602</v>
-      </c>
-      <c r="F36" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="37" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E37" t="s">
+        <v>603</v>
+      </c>
+      <c r="F37" t="s">
         <v>604</v>
-      </c>
-      <c r="F37" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="38" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E38" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F38" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="39" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E39" t="s">
+        <v>606</v>
+      </c>
+      <c r="F39" t="s">
         <v>607</v>
-      </c>
-      <c r="F39" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="40" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E40" t="s">
+        <v>608</v>
+      </c>
+      <c r="F40" t="s">
         <v>609</v>
-      </c>
-      <c r="F40" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="41" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E41" t="s">
+        <v>610</v>
+      </c>
+      <c r="F41" t="s">
         <v>611</v>
-      </c>
-      <c r="F41" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="42" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E42" t="s">
+        <v>612</v>
+      </c>
+      <c r="F42" t="s">
         <v>613</v>
-      </c>
-      <c r="F42" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="43" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E43" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F43" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="44" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E44" t="s">
+        <v>615</v>
+      </c>
+      <c r="F44" t="s">
         <v>616</v>
-      </c>
-      <c r="F44" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="45" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E45" t="s">
+        <v>617</v>
+      </c>
+      <c r="F45" t="s">
         <v>618</v>
-      </c>
-      <c r="F45" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="46" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E46" t="s">
+        <v>619</v>
+      </c>
+      <c r="F46" t="s">
         <v>620</v>
-      </c>
-      <c r="F46" t="s">
-        <v>621</v>
       </c>
     </row>
   </sheetData>
